--- a/backend/data/financials_by_company/1M4.F.xlsx
+++ b/backend/data/financials_by_company/1M4.F.xlsx
@@ -4746,10 +4746,8 @@
           <t>Sankt Gallen</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
+      <c r="C2" t="n">
+        <v>9000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
